--- a/doc/Formatos/Ejemplo_formato_cargar_monitorias.xlsx
+++ b/doc/Formatos/Ejemplo_formato_cargar_monitorias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebas\OneDrive\Documentos\PDG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41916108-8BA2-43C4-93E6-59364AFF0FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA77EA6-0E45-42B4-A375-A0297BD5A2FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FD5AF1D0-B680-4C7C-95F7-FEF857F7DD10}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10770" xr2:uid="{FD5AF1D0-B680-4C7C-95F7-FEF857F7DD10}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>FACULTAD</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>31-05-2025</t>
+  </si>
+  <si>
+    <t>Análisis de laboratorio en el proceso Salud Enfermedad</t>
   </si>
 </sst>
 </file>
@@ -497,11 +500,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB23B03E-F900-4CBF-98C8-2185B4E3447B}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -553,6 +558,32 @@
         <v>4.2</v>
       </c>
       <c r="H2" s="3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="H3" s="3">
         <v>4.5</v>
       </c>
     </row>
